--- a/backend/data/financials_by_company/1L2.SI.xlsx
+++ b/backend/data/financials_by_company/1L2.SI.xlsx
@@ -3630,10 +3630,8 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>638719</t>
-        </is>
+      <c r="C2" t="n">
+        <v>638719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3753,7 +3751,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AI2" t="n">
